--- a/output/yearly_benthic_cover_iteration_62_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_62_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.45962662534025</v>
+        <v>45.27145592610002</v>
       </c>
       <c r="M2" t="n">
-        <v>99.80388412324677</v>
+        <v>99.33245040817661</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.08813267885974</v>
+        <v>88.00494919587891</v>
       </c>
       <c r="C3" t="n">
-        <v>45.94986468917632</v>
+        <v>45.90064913134704</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228870490369512</v>
+        <v>2.228694511382098</v>
       </c>
       <c r="E3" t="n">
-        <v>5.721795655240112</v>
+        <v>5.68917955709966</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429568301231708</v>
+        <v>0.7428981704606992</v>
       </c>
       <c r="G3" t="n">
-        <v>33.97983429184102</v>
+        <v>33.96361308935279</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17601418566586</v>
+        <v>34.17331584119216</v>
       </c>
       <c r="I3" t="n">
-        <v>6.59518103735025</v>
+        <v>6.564134461012147</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643480188269818</v>
+        <v>4.64311356537937</v>
       </c>
       <c r="K3" t="n">
-        <v>11.91186732114024</v>
+        <v>11.99505080412107</v>
       </c>
       <c r="L3" t="n">
-        <v>48.90154966743558</v>
+        <v>48.86867748180505</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7632816777522</v>
+        <v>106.7643774172732</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.30156579484913</v>
+        <v>87.14218152046972</v>
       </c>
       <c r="C4" t="n">
-        <v>42.80288774986185</v>
+        <v>42.67330299469329</v>
       </c>
       <c r="D4" t="n">
-        <v>2.19165862455968</v>
+        <v>2.187359774255423</v>
       </c>
       <c r="E4" t="n">
-        <v>6.544191634615001</v>
+        <v>6.497261499246929</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7445191792084469</v>
+        <v>0.7444558764955518</v>
       </c>
       <c r="G4" t="n">
-        <v>33.41252764958802</v>
+        <v>33.33370306276512</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24788224358856</v>
+        <v>34.24497031879537</v>
       </c>
       <c r="I4" t="n">
-        <v>5.507541593236626</v>
+        <v>5.481581760814117</v>
       </c>
       <c r="J4" t="n">
-        <v>4.653244870052793</v>
+        <v>4.652849228097198</v>
       </c>
       <c r="K4" t="n">
-        <v>12.69843420515086</v>
+        <v>12.85781847953028</v>
       </c>
       <c r="L4" t="n">
-        <v>44.31547857172755</v>
+        <v>44.28654145741498</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81680052674027</v>
+        <v>99.81766293163855</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.22518252549855</v>
+        <v>86.07146422978545</v>
       </c>
       <c r="C5" t="n">
-        <v>42.58145015101454</v>
+        <v>42.45339372219183</v>
       </c>
       <c r="D5" t="n">
-        <v>2.139484186206693</v>
+        <v>2.135398804814713</v>
       </c>
       <c r="E5" t="n">
-        <v>7.154697119389911</v>
+        <v>7.105598377325242</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458425096257248</v>
+        <v>0.7457752025619825</v>
       </c>
       <c r="G5" t="n">
-        <v>32.61711186515164</v>
+        <v>32.54185731951987</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30875544278334</v>
+        <v>34.30565931785119</v>
       </c>
       <c r="I5" t="n">
-        <v>4.597775717180459</v>
+        <v>4.576080191700078</v>
       </c>
       <c r="J5" t="n">
-        <v>4.66151568516078</v>
+        <v>4.661095016012389</v>
       </c>
       <c r="K5" t="n">
-        <v>13.77481747450144</v>
+        <v>13.92853577021456</v>
       </c>
       <c r="L5" t="n">
-        <v>43.49074510800521</v>
+        <v>43.465804347571</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84701273352118</v>
+        <v>99.84773383997738</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.97417864050938</v>
+        <v>84.78822561408435</v>
       </c>
       <c r="C6" t="n">
-        <v>42.04471175610432</v>
+        <v>41.88095778181238</v>
       </c>
       <c r="D6" t="n">
-        <v>2.078747397068238</v>
+        <v>2.072923952341423</v>
       </c>
       <c r="E6" t="n">
-        <v>7.591127048333112</v>
+        <v>7.534232540566799</v>
       </c>
       <c r="F6" t="n">
-        <v>0.746965196572554</v>
+        <v>0.7468949371524972</v>
       </c>
       <c r="G6" t="n">
-        <v>31.69116033981154</v>
+        <v>31.5897879774092</v>
       </c>
       <c r="H6" t="n">
-        <v>34.36039904233748</v>
+        <v>34.35716710901487</v>
       </c>
       <c r="I6" t="n">
-        <v>3.837247137807998</v>
+        <v>3.819125740396455</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668532478578462</v>
+        <v>4.668093357203106</v>
       </c>
       <c r="K6" t="n">
-        <v>15.0258213594906</v>
+        <v>15.21177438591566</v>
       </c>
       <c r="L6" t="n">
-        <v>42.80175089226117</v>
+        <v>42.78015449361364</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87228400785609</v>
+        <v>99.87288666134168</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.60622820452521</v>
+        <v>83.29595073029205</v>
       </c>
       <c r="C7" t="n">
-        <v>41.27300053716345</v>
+        <v>40.98199865428826</v>
       </c>
       <c r="D7" t="n">
-        <v>2.01256196352189</v>
+        <v>2.000384246321365</v>
       </c>
       <c r="E7" t="n">
-        <v>7.883063763398009</v>
+        <v>7.801690874999615</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7479187236812506</v>
+        <v>0.7478474055135519</v>
       </c>
       <c r="G7" t="n">
-        <v>30.68214251030737</v>
+        <v>30.48433790504698</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40426128933753</v>
+        <v>34.40098065362339</v>
       </c>
       <c r="I7" t="n">
-        <v>3.201787931271359</v>
+        <v>3.186663360327437</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674492023007815</v>
+        <v>4.674046284459698</v>
       </c>
       <c r="K7" t="n">
-        <v>16.39377179547481</v>
+        <v>16.70404926970794</v>
       </c>
       <c r="L7" t="n">
-        <v>42.22663746908928</v>
+        <v>42.20786524988169</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89340980172753</v>
+        <v>99.89391317387791</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.58659361149085</v>
+        <v>88.21989604987472</v>
       </c>
       <c r="C8" t="n">
-        <v>43.65175342830938</v>
+        <v>43.32594553572955</v>
       </c>
       <c r="D8" t="n">
-        <v>2.016862812302104</v>
+        <v>2.004649578752892</v>
       </c>
       <c r="E8" t="n">
-        <v>9.769450937461642</v>
+        <v>9.662886211284443</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7495170274297797</v>
+        <v>0.7494420080497574</v>
       </c>
       <c r="G8" t="n">
-        <v>31.20920653200458</v>
+        <v>31.0013497692246</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47778326176986</v>
+        <v>34.47433237028883</v>
       </c>
       <c r="I8" t="n">
-        <v>5.679291619086767</v>
+        <v>5.643223561963209</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684481421436121</v>
+        <v>4.684012550310983</v>
       </c>
       <c r="K8" t="n">
-        <v>11.41340638850913</v>
+        <v>11.78010395012527</v>
       </c>
       <c r="L8" t="n">
-        <v>44.74593415509004</v>
+        <v>44.70624330201412</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81109397190855</v>
+        <v>99.81229278786896</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.82853614325977</v>
+        <v>86.28092145613751</v>
       </c>
       <c r="C9" t="n">
-        <v>42.77577034361794</v>
+        <v>42.26313402384714</v>
       </c>
       <c r="D9" t="n">
-        <v>1.937915653030342</v>
+        <v>1.917036478156818</v>
       </c>
       <c r="E9" t="n">
-        <v>10.1772662584867</v>
+        <v>10.02577792087589</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508812978936269</v>
+        <v>0.7508060815185902</v>
       </c>
       <c r="G9" t="n">
-        <v>29.9875675668758</v>
+        <v>29.64643746697831</v>
       </c>
       <c r="H9" t="n">
-        <v>34.54053970310684</v>
+        <v>34.53707974985515</v>
       </c>
       <c r="I9" t="n">
-        <v>4.741357552031283</v>
+        <v>4.711245749261579</v>
       </c>
       <c r="J9" t="n">
-        <v>4.693008111835167</v>
+        <v>4.692538009491187</v>
       </c>
       <c r="K9" t="n">
-        <v>13.17146385674023</v>
+        <v>13.71907854386249</v>
       </c>
       <c r="L9" t="n">
-        <v>43.89500769911163</v>
+        <v>43.86103122223582</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84224189946981</v>
+        <v>99.84324378994545</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>84.93388934950127</v>
+        <v>84.23150933680118</v>
       </c>
       <c r="C10" t="n">
-        <v>41.61750586475456</v>
+        <v>40.94498551559073</v>
       </c>
       <c r="D10" t="n">
-        <v>1.853582680694932</v>
+        <v>1.825405894022567</v>
       </c>
       <c r="E10" t="n">
-        <v>10.39392312086473</v>
+        <v>10.20192329497831</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520474748400694</v>
+        <v>0.7519744013042724</v>
       </c>
       <c r="G10" t="n">
-        <v>28.68258780572414</v>
+        <v>28.22939589601632</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59418384264319</v>
+        <v>34.59082245999652</v>
       </c>
       <c r="I10" t="n">
-        <v>3.957267706983778</v>
+        <v>3.932147382331499</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700296717750432</v>
+        <v>4.699840008151701</v>
       </c>
       <c r="K10" t="n">
-        <v>15.06611065049871</v>
+        <v>15.7684906631988</v>
       </c>
       <c r="L10" t="n">
-        <v>43.18467910830141</v>
+        <v>43.15565588373098</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86829562355469</v>
+        <v>99.86913206252052</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>82.87676309282109</v>
+        <v>82.02359121229375</v>
       </c>
       <c r="C11" t="n">
-        <v>40.17463534030256</v>
+        <v>39.34691294269341</v>
       </c>
       <c r="D11" t="n">
-        <v>1.762760580432261</v>
+        <v>1.727590320245397</v>
       </c>
       <c r="E11" t="n">
-        <v>10.43499071544672</v>
+        <v>10.20210633856226</v>
       </c>
       <c r="F11" t="n">
-        <v>0.753046282394797</v>
+        <v>0.7529770995955573</v>
       </c>
       <c r="G11" t="n">
-        <v>27.27719440589605</v>
+        <v>26.71670517556137</v>
       </c>
       <c r="H11" t="n">
-        <v>34.64012899016066</v>
+        <v>34.63694658139563</v>
       </c>
       <c r="I11" t="n">
-        <v>3.302102853523139</v>
+        <v>3.281158824461317</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706539264967479</v>
+        <v>4.706106872472231</v>
       </c>
       <c r="K11" t="n">
-        <v>17.12323690717889</v>
+        <v>17.97640878770623</v>
       </c>
       <c r="L11" t="n">
-        <v>42.59220364954678</v>
+        <v>42.56745195342447</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89007589702823</v>
+        <v>99.89077368382412</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>80.70517054981319</v>
+        <v>79.73590338208949</v>
       </c>
       <c r="C12" t="n">
-        <v>38.51502483748455</v>
+        <v>37.56740760715773</v>
       </c>
       <c r="D12" t="n">
-        <v>1.667683134301652</v>
+        <v>1.627184959886438</v>
       </c>
       <c r="E12" t="n">
-        <v>10.33130924106292</v>
+        <v>10.06541085838463</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7539031274228112</v>
+        <v>0.7538387861412014</v>
       </c>
       <c r="G12" t="n">
-        <v>25.80595321153896</v>
+        <v>25.16396412386615</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67954386144931</v>
+        <v>34.67658416249525</v>
       </c>
       <c r="I12" t="n">
-        <v>2.754883427644955</v>
+        <v>2.737428077933324</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711894546392568</v>
+        <v>4.711492413382507</v>
       </c>
       <c r="K12" t="n">
-        <v>19.29482945018683</v>
+        <v>20.26409661791049</v>
       </c>
       <c r="L12" t="n">
-        <v>42.09842063306409</v>
+        <v>42.07735247425229</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90827492073547</v>
+        <v>99.90885669932052</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>78.45728266850458</v>
+        <v>77.41971608161739</v>
       </c>
       <c r="C13" t="n">
-        <v>36.6935835313018</v>
+        <v>35.67440977196367</v>
       </c>
       <c r="D13" t="n">
-        <v>1.570053815127412</v>
+        <v>1.526426528879969</v>
       </c>
       <c r="E13" t="n">
-        <v>10.10949115284412</v>
+        <v>9.822713337645837</v>
       </c>
       <c r="F13" t="n">
-        <v>0.754639176564834</v>
+        <v>0.7545799152717148</v>
       </c>
       <c r="G13" t="n">
-        <v>24.2952239903432</v>
+        <v>23.60576293252723</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71340212198236</v>
+        <v>34.71067610249887</v>
       </c>
       <c r="I13" t="n">
-        <v>2.297977558112454</v>
+        <v>2.283432794345536</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716494853530211</v>
+        <v>4.716124470448215</v>
       </c>
       <c r="K13" t="n">
-        <v>21.54271733149539</v>
+        <v>22.58028391838264</v>
       </c>
       <c r="L13" t="n">
-        <v>41.687174597546</v>
+        <v>41.6692666408222</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92347546034321</v>
+        <v>99.9239603311685</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>84.67759850793986</v>
+        <v>83.9838072228257</v>
       </c>
       <c r="C14" t="n">
-        <v>40.53838196954</v>
+        <v>39.84174575679951</v>
       </c>
       <c r="D14" t="n">
-        <v>1.571880708265932</v>
+        <v>1.528117824759819</v>
       </c>
       <c r="E14" t="n">
-        <v>12.27428160844569</v>
+        <v>12.13465506661488</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555172643860552</v>
+        <v>0.7554159973743054</v>
       </c>
       <c r="G14" t="n">
-        <v>25.98387229507438</v>
+        <v>25.46770192132991</v>
       </c>
       <c r="H14" t="n">
-        <v>36.41417287625074</v>
+        <v>36.58491944630004</v>
       </c>
       <c r="I14" t="n">
-        <v>2.955890853104225</v>
+        <v>2.791646982857358</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721982902412843</v>
+        <v>4.721349983589407</v>
       </c>
       <c r="K14" t="n">
-        <v>15.32240149206012</v>
+        <v>16.01619277717429</v>
       </c>
       <c r="L14" t="n">
-        <v>44.04080135785401</v>
+        <v>44.04910955824228</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90158481945411</v>
+        <v>99.90704809221609</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>84.07057408492703</v>
+        <v>83.31252741256991</v>
       </c>
       <c r="C15" t="n">
-        <v>40.36886675416264</v>
+        <v>39.59046387271315</v>
       </c>
       <c r="D15" t="n">
-        <v>1.547043905913604</v>
+        <v>1.501909724196328</v>
       </c>
       <c r="E15" t="n">
-        <v>12.5115020590611</v>
+        <v>12.32651565867078</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7562558666533827</v>
+        <v>0.7561197795888052</v>
       </c>
       <c r="G15" t="n">
-        <v>25.59352998563711</v>
+        <v>25.04280310830316</v>
       </c>
       <c r="H15" t="n">
-        <v>36.4699926297378</v>
+        <v>36.63089067212589</v>
       </c>
       <c r="I15" t="n">
-        <v>2.465650471340399</v>
+        <v>2.328539847254912</v>
       </c>
       <c r="J15" t="n">
-        <v>4.72659916658364</v>
+        <v>4.72574862243003</v>
       </c>
       <c r="K15" t="n">
-        <v>15.92942591507296</v>
+        <v>16.68747258743009</v>
       </c>
       <c r="L15" t="n">
-        <v>43.61959925151148</v>
+        <v>43.64451779033295</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91789192074708</v>
+        <v>99.92245425047619</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>81.78156059013632</v>
+        <v>80.93848474911435</v>
       </c>
       <c r="C16" t="n">
-        <v>38.46176977682729</v>
+        <v>37.57671391942226</v>
       </c>
       <c r="D16" t="n">
-        <v>1.458958842451269</v>
+        <v>1.411309110426516</v>
       </c>
       <c r="E16" t="n">
-        <v>12.1418648705216</v>
+        <v>11.90660272674467</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7568897454697089</v>
+        <v>0.7567245129198549</v>
       </c>
       <c r="G16" t="n">
-        <v>24.13629421851213</v>
+        <v>23.53213086510765</v>
       </c>
       <c r="H16" t="n">
-        <v>36.50056106137439</v>
+        <v>36.66018751256501</v>
       </c>
       <c r="I16" t="n">
-        <v>2.05643094262154</v>
+        <v>1.942001815601553</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730560909185678</v>
+        <v>4.729528205749091</v>
       </c>
       <c r="K16" t="n">
-        <v>18.2184394098637</v>
+        <v>19.06151525088564</v>
       </c>
       <c r="L16" t="n">
-        <v>43.25130052243844</v>
+        <v>43.29708916726835</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93150970912941</v>
+        <v>99.93531833757626</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>83.46161561893685</v>
+        <v>82.60546289849432</v>
       </c>
       <c r="C17" t="n">
-        <v>39.6883655762419</v>
+        <v>38.80390338526615</v>
       </c>
       <c r="D17" t="n">
-        <v>1.460152761529247</v>
+        <v>1.412396955344924</v>
       </c>
       <c r="E17" t="n">
-        <v>12.92021783116316</v>
+        <v>12.6739917436199</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7575091358738438</v>
+        <v>0.7573078003867417</v>
       </c>
       <c r="G17" t="n">
-        <v>24.58296428055291</v>
+        <v>23.99011715064697</v>
       </c>
       <c r="H17" t="n">
-        <v>36.95734925261757</v>
+        <v>37.12829297724588</v>
       </c>
       <c r="I17" t="n">
-        <v>2.048990257988595</v>
+        <v>1.910182518832781</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734432099211521</v>
+        <v>4.733173752417134</v>
       </c>
       <c r="K17" t="n">
-        <v>16.53838438106317</v>
+        <v>17.39453710150569</v>
       </c>
       <c r="L17" t="n">
-        <v>43.70500621383559</v>
+        <v>43.73793580410953</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93175617114065</v>
+        <v>99.93637629088137</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>81.2207077616542</v>
+        <v>80.27700278094692</v>
       </c>
       <c r="C18" t="n">
-        <v>37.76451813211271</v>
+        <v>36.77065666006682</v>
       </c>
       <c r="D18" t="n">
-        <v>1.377139684128922</v>
+        <v>1.326902889754985</v>
       </c>
       <c r="E18" t="n">
-        <v>12.47045496958754</v>
+        <v>12.1722985678687</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7580403418373336</v>
+        <v>0.7578086885819915</v>
       </c>
       <c r="G18" t="n">
-        <v>23.1853656386042</v>
+        <v>22.53796686001789</v>
       </c>
       <c r="H18" t="n">
-        <v>36.98326572462832</v>
+        <v>37.15284986633718</v>
       </c>
       <c r="I18" t="n">
-        <v>1.708689266384543</v>
+        <v>1.592871604748733</v>
       </c>
       <c r="J18" t="n">
-        <v>4.737752136483332</v>
+        <v>4.736304303637445</v>
       </c>
       <c r="K18" t="n">
-        <v>18.77929223834581</v>
+        <v>19.72299721905306</v>
       </c>
       <c r="L18" t="n">
-        <v>43.39927323348626</v>
+        <v>43.45328549535699</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94308360394479</v>
+        <v>99.94693937447687</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>80.3285936228051</v>
+        <v>79.31643137468073</v>
       </c>
       <c r="C19" t="n">
-        <v>37.13620444897344</v>
+        <v>36.05563776728357</v>
       </c>
       <c r="D19" t="n">
-        <v>1.344759331521024</v>
+        <v>1.292255148676178</v>
       </c>
       <c r="E19" t="n">
-        <v>12.41469843550382</v>
+        <v>12.07581434240639</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7584885083806995</v>
+        <v>0.7582316658437335</v>
       </c>
       <c r="G19" t="n">
-        <v>22.64021373907419</v>
+        <v>21.9494613663319</v>
       </c>
       <c r="H19" t="n">
-        <v>37.00513087011915</v>
+        <v>37.17358704042762</v>
       </c>
       <c r="I19" t="n">
-        <v>1.424749560826842</v>
+        <v>1.328133899471579</v>
       </c>
       <c r="J19" t="n">
-        <v>4.740553177379368</v>
+        <v>4.738947911523332</v>
       </c>
       <c r="K19" t="n">
-        <v>19.67140637719489</v>
+        <v>20.68356862531927</v>
       </c>
       <c r="L19" t="n">
-        <v>43.14492558309878</v>
+        <v>43.2165471739319</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95253640926711</v>
+        <v>99.95575356653474</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>77.81792113134952</v>
+        <v>76.77271325550021</v>
       </c>
       <c r="C20" t="n">
-        <v>34.84536940647232</v>
+        <v>33.71650744567096</v>
       </c>
       <c r="D20" t="n">
-        <v>1.252641430558523</v>
+        <v>1.199757996600445</v>
       </c>
       <c r="E20" t="n">
-        <v>11.76225674709257</v>
+        <v>11.39600237371636</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7588744541991291</v>
+        <v>0.7585962041209923</v>
       </c>
       <c r="G20" t="n">
-        <v>21.08932733278543</v>
+        <v>20.37836090055942</v>
       </c>
       <c r="H20" t="n">
-        <v>37.0239603914131</v>
+        <v>37.19145914467978</v>
       </c>
       <c r="I20" t="n">
-        <v>1.187895436556218</v>
+        <v>1.107310360067001</v>
       </c>
       <c r="J20" t="n">
-        <v>4.742965338744554</v>
+        <v>4.741226275756199</v>
       </c>
       <c r="K20" t="n">
-        <v>22.18207886865047</v>
+        <v>23.2272867444998</v>
       </c>
       <c r="L20" t="n">
-        <v>42.93297534818755</v>
+        <v>43.0193132015106</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96042362331036</v>
+        <v>99.96310739168135</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>83.37352339743475</v>
+        <v>82.52078715900301</v>
       </c>
       <c r="C21" t="n">
-        <v>38.23445844508196</v>
+        <v>37.34283764004093</v>
       </c>
       <c r="D21" t="n">
-        <v>1.253531119402504</v>
+        <v>1.200493145785921</v>
       </c>
       <c r="E21" t="n">
-        <v>13.60552754379155</v>
+        <v>13.33556247576827</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7594134449425396</v>
+        <v>0.7590610323473054</v>
       </c>
       <c r="G21" t="n">
-        <v>22.64314236923394</v>
+        <v>22.07060273125155</v>
       </c>
       <c r="H21" t="n">
-        <v>38.58909300439975</v>
+        <v>38.8940031659091</v>
       </c>
       <c r="I21" t="n">
-        <v>1.776481884773596</v>
+        <v>1.51693315577021</v>
       </c>
       <c r="J21" t="n">
-        <v>4.746334030890869</v>
+        <v>4.744131452170657</v>
       </c>
       <c r="K21" t="n">
-        <v>16.62647660256524</v>
+        <v>17.47921284099698</v>
       </c>
       <c r="L21" t="n">
-        <v>45.07989091789764</v>
+        <v>45.12741604471633</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94082596554483</v>
+        <v>99.94946652575425</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_62_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_62_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.27145592610002</v>
+        <v>45.15393832730517</v>
       </c>
       <c r="M2" t="n">
-        <v>99.33245040817661</v>
+        <v>100.592703788641</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.00494919587891</v>
+        <v>88.00627455527966</v>
       </c>
       <c r="C3" t="n">
-        <v>45.90064913134704</v>
+        <v>45.87747497678829</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228694511382098</v>
+        <v>2.228715492672557</v>
       </c>
       <c r="E3" t="n">
-        <v>5.68917955709966</v>
+        <v>5.676109456454713</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7428981704606992</v>
+        <v>0.7429051642241856</v>
       </c>
       <c r="G3" t="n">
-        <v>33.96361308935279</v>
+        <v>33.95553623892588</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17331584119216</v>
+        <v>34.17363755431253</v>
       </c>
       <c r="I3" t="n">
-        <v>6.564134461012147</v>
+        <v>6.586213372288634</v>
       </c>
       <c r="J3" t="n">
-        <v>4.64311356537937</v>
+        <v>4.64315727640116</v>
       </c>
       <c r="K3" t="n">
-        <v>11.99505080412107</v>
+        <v>11.99372544472034</v>
       </c>
       <c r="L3" t="n">
-        <v>48.86867748180505</v>
+        <v>48.89238668886261</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7643774172732</v>
+        <v>106.7635871103712</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.14218152046972</v>
+        <v>87.12698262147541</v>
       </c>
       <c r="C4" t="n">
-        <v>42.67330299469329</v>
+        <v>42.63872627573539</v>
       </c>
       <c r="D4" t="n">
-        <v>2.187359774255423</v>
+        <v>2.186491746429898</v>
       </c>
       <c r="E4" t="n">
-        <v>6.497261499246929</v>
+        <v>6.485250407425583</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444558764955518</v>
+        <v>0.7444684086727285</v>
       </c>
       <c r="G4" t="n">
-        <v>33.33370306276512</v>
+        <v>33.31223746418341</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24497031879537</v>
+        <v>34.2455467989455</v>
       </c>
       <c r="I4" t="n">
-        <v>5.481581760814117</v>
+        <v>5.50006024161374</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652849228097198</v>
+        <v>4.652927554204553</v>
       </c>
       <c r="K4" t="n">
-        <v>12.85781847953028</v>
+        <v>12.8730173785246</v>
       </c>
       <c r="L4" t="n">
-        <v>44.28654145741498</v>
+        <v>44.30530597428756</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81766293163855</v>
+        <v>99.81704962854754</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.07146422978545</v>
+        <v>85.910230038837</v>
       </c>
       <c r="C5" t="n">
-        <v>42.45339372219183</v>
+        <v>42.27559269985291</v>
       </c>
       <c r="D5" t="n">
-        <v>2.135398804814713</v>
+        <v>2.126906663807638</v>
       </c>
       <c r="E5" t="n">
-        <v>7.105598377325242</v>
+        <v>7.073776055746009</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457752025619825</v>
+        <v>0.7457947013050362</v>
       </c>
       <c r="G5" t="n">
-        <v>32.54185731951987</v>
+        <v>32.4044305059012</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30565931785119</v>
+        <v>34.30655626003166</v>
       </c>
       <c r="I5" t="n">
-        <v>4.576080191700078</v>
+        <v>4.591548968888981</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661095016012389</v>
+        <v>4.661216883156476</v>
       </c>
       <c r="K5" t="n">
-        <v>13.92853577021456</v>
+        <v>14.089769961163</v>
       </c>
       <c r="L5" t="n">
-        <v>43.465804347571</v>
+        <v>43.48185788782817</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84773383997738</v>
+        <v>99.84722054884409</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.78822561408435</v>
+        <v>84.55855782365855</v>
       </c>
       <c r="C6" t="n">
-        <v>41.88095778181238</v>
+        <v>41.63695084614936</v>
       </c>
       <c r="D6" t="n">
-        <v>2.072923952341423</v>
+        <v>2.060916010707689</v>
       </c>
       <c r="E6" t="n">
-        <v>7.534232540566799</v>
+        <v>7.492979411325638</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468949371524972</v>
+        <v>0.7469213123482593</v>
       </c>
       <c r="G6" t="n">
-        <v>31.5897879774092</v>
+        <v>31.39903164717173</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35716710901487</v>
+        <v>34.35838036801993</v>
       </c>
       <c r="I6" t="n">
-        <v>3.819125740396455</v>
+        <v>3.832070871908701</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668093357203106</v>
+        <v>4.668258202176621</v>
       </c>
       <c r="K6" t="n">
-        <v>15.21177438591566</v>
+        <v>15.44144217634143</v>
       </c>
       <c r="L6" t="n">
-        <v>42.78015449361364</v>
+        <v>42.79406395059562</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87288666134168</v>
+        <v>99.87245697308643</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.29595073029205</v>
+        <v>83.05017069743664</v>
       </c>
       <c r="C7" t="n">
-        <v>40.98199865428826</v>
+        <v>40.72369332087425</v>
       </c>
       <c r="D7" t="n">
-        <v>2.000384246321365</v>
+        <v>1.987555377374087</v>
       </c>
       <c r="E7" t="n">
-        <v>7.801690874999615</v>
+        <v>7.759173454709617</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478474055135519</v>
+        <v>0.7478798790784109</v>
       </c>
       <c r="G7" t="n">
-        <v>30.48433790504698</v>
+        <v>30.28134764853689</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40098065362339</v>
+        <v>34.40247443760691</v>
       </c>
       <c r="I7" t="n">
-        <v>3.186663360327437</v>
+        <v>3.197490655890662</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674046284459698</v>
+        <v>4.674249244240069</v>
       </c>
       <c r="K7" t="n">
-        <v>16.70404926970794</v>
+        <v>16.94982930256336</v>
       </c>
       <c r="L7" t="n">
-        <v>42.20786524988169</v>
+        <v>42.2200309634538</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89391317387791</v>
+        <v>99.89355358689141</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.21989604987472</v>
+        <v>87.96053882714415</v>
       </c>
       <c r="C8" t="n">
-        <v>43.32594553572955</v>
+        <v>43.0696515501382</v>
       </c>
       <c r="D8" t="n">
-        <v>2.004649578752892</v>
+        <v>1.99180239362235</v>
       </c>
       <c r="E8" t="n">
-        <v>9.662886211284443</v>
+        <v>9.6214082487264</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494420080497574</v>
+        <v>0.7494779517833793</v>
       </c>
       <c r="G8" t="n">
-        <v>31.0013497692246</v>
+        <v>30.79899435901638</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47433237028883</v>
+        <v>34.47598578203545</v>
       </c>
       <c r="I8" t="n">
-        <v>5.643223561963209</v>
+        <v>5.63863289331406</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684012550310983</v>
+        <v>4.684237198646121</v>
       </c>
       <c r="K8" t="n">
-        <v>11.78010395012527</v>
+        <v>12.03946117285585</v>
       </c>
       <c r="L8" t="n">
-        <v>44.70624330201412</v>
+        <v>44.70333361264599</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81229278786896</v>
+        <v>99.81244633564003</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.28092145613751</v>
+        <v>85.96038425106077</v>
       </c>
       <c r="C9" t="n">
-        <v>42.26313402384714</v>
+        <v>41.94467183446986</v>
       </c>
       <c r="D9" t="n">
-        <v>1.917036478156818</v>
+        <v>1.901333654248666</v>
       </c>
       <c r="E9" t="n">
-        <v>10.02577792087589</v>
+        <v>9.968971725379417</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508060815185902</v>
+        <v>0.7508460708140217</v>
       </c>
       <c r="G9" t="n">
-        <v>29.64643746697831</v>
+        <v>29.40008741796683</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53707974985515</v>
+        <v>34.538919257445</v>
       </c>
       <c r="I9" t="n">
-        <v>4.711245749261579</v>
+        <v>4.707438182619186</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692538009491187</v>
+        <v>4.692787942587636</v>
       </c>
       <c r="K9" t="n">
-        <v>13.71907854386249</v>
+        <v>14.03961574893923</v>
       </c>
       <c r="L9" t="n">
-        <v>43.86103122223582</v>
+        <v>43.85908372510996</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84324378994545</v>
+        <v>99.84337130851905</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>84.23150933680118</v>
+        <v>83.65300471942717</v>
       </c>
       <c r="C10" t="n">
-        <v>40.94498551559073</v>
+        <v>40.36767019547244</v>
       </c>
       <c r="D10" t="n">
-        <v>1.825405894022567</v>
+        <v>1.797842604162992</v>
       </c>
       <c r="E10" t="n">
-        <v>10.20192329497831</v>
+        <v>10.08118740613291</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7519744013042724</v>
+        <v>0.7520215931643178</v>
       </c>
       <c r="G10" t="n">
-        <v>28.22939589601632</v>
+        <v>27.79981809506445</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59082245999652</v>
+        <v>34.59299328555863</v>
       </c>
       <c r="I10" t="n">
-        <v>3.932147382331499</v>
+        <v>3.929006778066892</v>
       </c>
       <c r="J10" t="n">
-        <v>4.699840008151701</v>
+        <v>4.700134957276988</v>
       </c>
       <c r="K10" t="n">
-        <v>15.7684906631988</v>
+        <v>16.34699528057283</v>
       </c>
       <c r="L10" t="n">
-        <v>43.15565588373098</v>
+        <v>43.15457235221529</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86913206252052</v>
+        <v>99.86923782826057</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>82.02359121229375</v>
+        <v>81.13427284394655</v>
       </c>
       <c r="C11" t="n">
-        <v>39.34691294269341</v>
+        <v>38.4578332088867</v>
       </c>
       <c r="D11" t="n">
-        <v>1.727590320245397</v>
+        <v>1.685987176848353</v>
       </c>
       <c r="E11" t="n">
-        <v>10.20210633856226</v>
+        <v>10.00040189935593</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7529770995955573</v>
+        <v>0.7530345497479501</v>
       </c>
       <c r="G11" t="n">
-        <v>26.71670517556137</v>
+        <v>26.07021144034823</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63694658139563</v>
+        <v>34.63958928840572</v>
       </c>
       <c r="I11" t="n">
-        <v>3.281158824461317</v>
+        <v>3.278582553315694</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706106872472231</v>
+        <v>4.70646593592469</v>
       </c>
       <c r="K11" t="n">
-        <v>17.97640878770623</v>
+        <v>18.86572715605343</v>
       </c>
       <c r="L11" t="n">
-        <v>42.56745195342447</v>
+        <v>42.56730055789136</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89077368382412</v>
+        <v>99.89086092283148</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>79.73590338208949</v>
+        <v>78.48393112753143</v>
       </c>
       <c r="C12" t="n">
-        <v>37.56740760715773</v>
+        <v>36.31465203784583</v>
       </c>
       <c r="D12" t="n">
-        <v>1.627184959886438</v>
+        <v>1.569459722199928</v>
       </c>
       <c r="E12" t="n">
-        <v>10.06541085838463</v>
+        <v>9.765109141593664</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538387861412014</v>
+        <v>0.7539093764279071</v>
       </c>
       <c r="G12" t="n">
-        <v>25.16396412386615</v>
+        <v>24.26836180411978</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67658416249525</v>
+        <v>34.67983131568374</v>
       </c>
       <c r="I12" t="n">
-        <v>2.737428077933324</v>
+        <v>2.735326164831986</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711492413382507</v>
+        <v>4.711933602674422</v>
       </c>
       <c r="K12" t="n">
-        <v>20.26409661791049</v>
+        <v>21.51606887246858</v>
       </c>
       <c r="L12" t="n">
-        <v>42.07735247425229</v>
+        <v>42.07820735209349</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90885669932052</v>
+        <v>99.9089282624079</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>77.41971608161739</v>
+        <v>75.74488016711655</v>
       </c>
       <c r="C13" t="n">
-        <v>35.67440977196367</v>
+        <v>33.99769549570864</v>
       </c>
       <c r="D13" t="n">
-        <v>1.526426528879969</v>
+        <v>1.450170702648236</v>
       </c>
       <c r="E13" t="n">
-        <v>9.822713337645837</v>
+        <v>9.403186011942259</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7545799152717148</v>
+        <v>0.7546663981639939</v>
       </c>
       <c r="G13" t="n">
-        <v>23.60576293252723</v>
+        <v>22.42381043093687</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71067610249887</v>
+        <v>34.71465431554373</v>
       </c>
       <c r="I13" t="n">
-        <v>2.283432794345536</v>
+        <v>2.28172731935649</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716124470448215</v>
+        <v>4.716664988524965</v>
       </c>
       <c r="K13" t="n">
-        <v>22.58028391838264</v>
+        <v>24.25511983288344</v>
       </c>
       <c r="L13" t="n">
-        <v>41.6692666408222</v>
+        <v>41.67120338905148</v>
       </c>
       <c r="M13" t="n">
-        <v>99.9239603311685</v>
+        <v>99.92401871764358</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.9838072228257</v>
+        <v>82.78997256203047</v>
       </c>
       <c r="C14" t="n">
-        <v>39.84174575679951</v>
+        <v>38.44556801251279</v>
       </c>
       <c r="D14" t="n">
-        <v>1.528117824759819</v>
+        <v>1.451835869295064</v>
       </c>
       <c r="E14" t="n">
-        <v>12.13465506661488</v>
+        <v>11.86104468155029</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7554159973743054</v>
+        <v>0.7555329480904331</v>
       </c>
       <c r="G14" t="n">
-        <v>25.46770192132991</v>
+        <v>24.42129985278147</v>
       </c>
       <c r="H14" t="n">
-        <v>36.58491944630004</v>
+        <v>36.72625676784788</v>
       </c>
       <c r="I14" t="n">
-        <v>2.791646982857358</v>
+        <v>2.851921516900128</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721349983589407</v>
+        <v>4.722080925565209</v>
       </c>
       <c r="K14" t="n">
-        <v>16.01619277717429</v>
+        <v>17.21002743796954</v>
       </c>
       <c r="L14" t="n">
-        <v>44.04910955824228</v>
+        <v>44.24944953158648</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90704809221609</v>
+        <v>99.90504498206882</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>83.31252741256991</v>
+        <v>81.70598565186337</v>
       </c>
       <c r="C15" t="n">
-        <v>39.59046387271315</v>
+        <v>37.80182665223076</v>
       </c>
       <c r="D15" t="n">
-        <v>1.501909724196328</v>
+        <v>1.41149764363845</v>
       </c>
       <c r="E15" t="n">
-        <v>12.32651565867078</v>
+        <v>11.92797863437796</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7561197795888052</v>
+        <v>0.7562662045356181</v>
       </c>
       <c r="G15" t="n">
-        <v>25.04280310830316</v>
+        <v>23.74277142878843</v>
       </c>
       <c r="H15" t="n">
-        <v>36.63089067212589</v>
+        <v>36.76190016970164</v>
       </c>
       <c r="I15" t="n">
-        <v>2.328539847254912</v>
+        <v>2.378907792473668</v>
       </c>
       <c r="J15" t="n">
-        <v>4.72574862243003</v>
+        <v>4.726663778347615</v>
       </c>
       <c r="K15" t="n">
-        <v>16.68747258743009</v>
+        <v>18.29401434813662</v>
       </c>
       <c r="L15" t="n">
-        <v>43.64451779033295</v>
+        <v>43.82493895749653</v>
       </c>
       <c r="M15" t="n">
-        <v>99.92245425047619</v>
+        <v>99.9207799578639</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>80.93848474911435</v>
+        <v>78.95492241754594</v>
       </c>
       <c r="C16" t="n">
-        <v>37.57671391942226</v>
+        <v>35.4178545370888</v>
       </c>
       <c r="D16" t="n">
-        <v>1.411309110426516</v>
+        <v>1.307875866920306</v>
       </c>
       <c r="E16" t="n">
-        <v>11.90660272674467</v>
+        <v>11.38299478335235</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7567245129198549</v>
+        <v>0.7568996864527151</v>
       </c>
       <c r="G16" t="n">
-        <v>23.53213086510765</v>
+        <v>21.99975175691568</v>
       </c>
       <c r="H16" t="n">
-        <v>36.66018751256501</v>
+        <v>36.79269355813545</v>
       </c>
       <c r="I16" t="n">
-        <v>1.942001815601553</v>
+        <v>1.984083725439958</v>
       </c>
       <c r="J16" t="n">
-        <v>4.729528205749091</v>
+        <v>4.730623040329471</v>
       </c>
       <c r="K16" t="n">
-        <v>19.06151525088564</v>
+        <v>21.04507758245407</v>
       </c>
       <c r="L16" t="n">
-        <v>43.29708916726835</v>
+        <v>43.47098710844398</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93531833757626</v>
+        <v>99.93391922798685</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>82.60546289849432</v>
+        <v>80.58357313655208</v>
       </c>
       <c r="C17" t="n">
-        <v>38.80390338526615</v>
+        <v>36.61339154664928</v>
       </c>
       <c r="D17" t="n">
-        <v>1.412396955344924</v>
+        <v>1.30893819196274</v>
       </c>
       <c r="E17" t="n">
-        <v>12.6739917436199</v>
+        <v>12.1392843225634</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7573078003867417</v>
+        <v>0.7575144798837026</v>
       </c>
       <c r="G17" t="n">
-        <v>23.99011715064697</v>
+        <v>22.43739385985436</v>
       </c>
       <c r="H17" t="n">
-        <v>37.12829297724588</v>
+        <v>37.24235126050844</v>
       </c>
       <c r="I17" t="n">
-        <v>1.910182518832781</v>
+        <v>1.963625522506311</v>
       </c>
       <c r="J17" t="n">
-        <v>4.733173752417134</v>
+        <v>4.734465499273143</v>
       </c>
       <c r="K17" t="n">
-        <v>17.39453710150569</v>
+        <v>19.41642686344791</v>
       </c>
       <c r="L17" t="n">
-        <v>43.73793580410953</v>
+        <v>43.9047805279753</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93637629088137</v>
+        <v>99.9345989380725</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>80.27700278094692</v>
+        <v>77.90211581446572</v>
       </c>
       <c r="C18" t="n">
-        <v>36.77065666006682</v>
+        <v>34.23439929919262</v>
       </c>
       <c r="D18" t="n">
-        <v>1.326902889754985</v>
+        <v>1.211979862520295</v>
       </c>
       <c r="E18" t="n">
-        <v>12.1722985678687</v>
+        <v>11.5129954446057</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7578086885819915</v>
+        <v>0.758045244596838</v>
       </c>
       <c r="G18" t="n">
-        <v>22.53796686001789</v>
+        <v>20.77536563036896</v>
       </c>
       <c r="H18" t="n">
-        <v>37.15284986633718</v>
+        <v>37.26844571336471</v>
       </c>
       <c r="I18" t="n">
-        <v>1.592871604748733</v>
+        <v>1.637501140278989</v>
       </c>
       <c r="J18" t="n">
-        <v>4.736304303637445</v>
+        <v>4.73778277873024</v>
       </c>
       <c r="K18" t="n">
-        <v>19.72299721905306</v>
+        <v>22.09788418553427</v>
       </c>
       <c r="L18" t="n">
-        <v>43.45328549535699</v>
+        <v>43.61317136187017</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94693937447687</v>
+        <v>99.94545484659706</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>79.31643137468073</v>
+        <v>76.79417426031505</v>
       </c>
       <c r="C19" t="n">
-        <v>36.05563776728357</v>
+        <v>33.35734072509594</v>
       </c>
       <c r="D19" t="n">
-        <v>1.292255148676178</v>
+        <v>1.171738017917711</v>
       </c>
       <c r="E19" t="n">
-        <v>12.07581434240639</v>
+        <v>11.36160641791053</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7582316658437335</v>
+        <v>0.7585010568262801</v>
       </c>
       <c r="G19" t="n">
-        <v>21.9494613663319</v>
+        <v>20.08555298486786</v>
       </c>
       <c r="H19" t="n">
-        <v>37.17358704042762</v>
+        <v>37.29085521127995</v>
       </c>
       <c r="I19" t="n">
-        <v>1.328133899471579</v>
+        <v>1.38528896634845</v>
       </c>
       <c r="J19" t="n">
-        <v>4.738947911523332</v>
+        <v>4.740631605164253</v>
       </c>
       <c r="K19" t="n">
-        <v>20.68356862531927</v>
+        <v>23.20582573968496</v>
       </c>
       <c r="L19" t="n">
-        <v>43.2165471739319</v>
+        <v>43.39068498544091</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95575356653474</v>
+        <v>99.9538514502218</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>76.77271325550021</v>
+        <v>74.03500178996049</v>
       </c>
       <c r="C20" t="n">
-        <v>33.71650744567096</v>
+        <v>30.81062725249402</v>
       </c>
       <c r="D20" t="n">
-        <v>1.199757996600445</v>
+        <v>1.073180650264819</v>
       </c>
       <c r="E20" t="n">
-        <v>11.39600237371636</v>
+        <v>10.5984589256669</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7585962041209923</v>
+        <v>0.7588954984699563</v>
       </c>
       <c r="G20" t="n">
-        <v>20.37836090055942</v>
+        <v>18.39611456111581</v>
       </c>
       <c r="H20" t="n">
-        <v>37.19145914467978</v>
+        <v>37.31024749305893</v>
       </c>
       <c r="I20" t="n">
-        <v>1.107310360067001</v>
+        <v>1.155007795946854</v>
       </c>
       <c r="J20" t="n">
-        <v>4.741226275756199</v>
+        <v>4.74309686543723</v>
       </c>
       <c r="K20" t="n">
-        <v>23.2272867444998</v>
+        <v>25.9649982100395</v>
       </c>
       <c r="L20" t="n">
-        <v>43.0193132015106</v>
+        <v>43.18589428840125</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96310739168135</v>
+        <v>99.96151975093477</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>82.52078715900301</v>
+        <v>80.42305738690773</v>
       </c>
       <c r="C21" t="n">
-        <v>37.34283764004093</v>
+        <v>34.87410597911746</v>
       </c>
       <c r="D21" t="n">
-        <v>1.200493145785921</v>
+        <v>1.073870252158604</v>
       </c>
       <c r="E21" t="n">
-        <v>13.33556247576827</v>
+        <v>12.75949297955173</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7590610323473054</v>
+        <v>0.7593831477513708</v>
       </c>
       <c r="G21" t="n">
-        <v>22.07060273125155</v>
+        <v>20.30376892051084</v>
       </c>
       <c r="H21" t="n">
-        <v>38.8940031659091</v>
+        <v>39.23005565143082</v>
       </c>
       <c r="I21" t="n">
-        <v>1.51693315577021</v>
+        <v>1.550341762058316</v>
       </c>
       <c r="J21" t="n">
-        <v>4.744131452170657</v>
+        <v>4.746144673446071</v>
       </c>
       <c r="K21" t="n">
-        <v>17.47921284099698</v>
+        <v>19.57694261309226</v>
       </c>
       <c r="L21" t="n">
-        <v>45.12741604471633</v>
+        <v>45.49730653489574</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94946652575425</v>
+        <v>99.94835512710546</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_62_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_62_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.15393832730517</v>
+        <v>43.41888284583241</v>
       </c>
       <c r="M2" t="n">
-        <v>100.592703788641</v>
+        <v>97.07978523864546</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.00627455527966</v>
+        <v>81.57200222889031</v>
       </c>
       <c r="C3" t="n">
-        <v>45.87747497678829</v>
+        <v>43.32755778444588</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228715492672557</v>
+        <v>2.185605683689522</v>
       </c>
       <c r="E3" t="n">
-        <v>5.676109456454713</v>
+        <v>4.154967825033306</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429051642241856</v>
+        <v>0.7377000271931077</v>
       </c>
       <c r="G3" t="n">
-        <v>33.95553623892588</v>
+        <v>32.8751521588299</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17363755431253</v>
+        <v>33.93420125088295</v>
       </c>
       <c r="I3" t="n">
-        <v>6.586213372288634</v>
+        <v>3.073750113304615</v>
       </c>
       <c r="J3" t="n">
-        <v>4.64315727640116</v>
+        <v>4.610625169956923</v>
       </c>
       <c r="K3" t="n">
-        <v>11.99372544472034</v>
+        <v>18.42799777110968</v>
       </c>
       <c r="L3" t="n">
-        <v>48.89238668886261</v>
+        <v>45.13333333333333</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7635871103712</v>
+        <v>106.8888888888889</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.12698262147541</v>
+        <v>88.78958095521006</v>
       </c>
       <c r="C4" t="n">
-        <v>42.63872627573539</v>
+        <v>42.98684026793355</v>
       </c>
       <c r="D4" t="n">
-        <v>2.186491746429898</v>
+        <v>2.191384070813287</v>
       </c>
       <c r="E4" t="n">
-        <v>6.485250407425583</v>
+        <v>6.584817937053163</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444684086727285</v>
+        <v>0.7396503864780165</v>
       </c>
       <c r="G4" t="n">
-        <v>33.31223746418341</v>
+        <v>33.58463811075183</v>
       </c>
       <c r="H4" t="n">
-        <v>34.2455467989455</v>
+        <v>34.02391777798876</v>
       </c>
       <c r="I4" t="n">
-        <v>5.50006024161374</v>
+        <v>7.042357756637394</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652927554204553</v>
+        <v>4.622814915487603</v>
       </c>
       <c r="K4" t="n">
-        <v>12.8730173785246</v>
+        <v>11.21041904478994</v>
       </c>
       <c r="L4" t="n">
-        <v>44.30530597428756</v>
+        <v>45.56861442061726</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81704962854754</v>
+        <v>99.76587373334075</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.910230038837</v>
+        <v>87.85604685863919</v>
       </c>
       <c r="C5" t="n">
-        <v>42.27559269985291</v>
+        <v>43.14506165250285</v>
       </c>
       <c r="D5" t="n">
-        <v>2.126906663807638</v>
+        <v>2.147873552162331</v>
       </c>
       <c r="E5" t="n">
-        <v>7.073776055746009</v>
+        <v>7.434362572075559</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457947013050362</v>
+        <v>0.7413009737642189</v>
       </c>
       <c r="G5" t="n">
-        <v>32.4044305059012</v>
+        <v>32.91780611066289</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30655626003166</v>
+        <v>34.09984479315407</v>
       </c>
       <c r="I5" t="n">
-        <v>4.591548968888981</v>
+        <v>5.881727770793756</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661216883156476</v>
+        <v>4.633131086026368</v>
       </c>
       <c r="K5" t="n">
-        <v>14.089769961163</v>
+        <v>12.14395314136081</v>
       </c>
       <c r="L5" t="n">
-        <v>43.48185788782817</v>
+        <v>44.51536415734085</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84722054884409</v>
+        <v>99.80437895120451</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.55855782365855</v>
+        <v>86.68721580798749</v>
       </c>
       <c r="C6" t="n">
-        <v>41.63695084614936</v>
+        <v>42.88941879284575</v>
       </c>
       <c r="D6" t="n">
-        <v>2.060916010707689</v>
+        <v>2.092747239372875</v>
       </c>
       <c r="E6" t="n">
-        <v>7.492979411325638</v>
+        <v>8.062004901733181</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469213123482593</v>
+        <v>0.7427007584305091</v>
       </c>
       <c r="G6" t="n">
-        <v>31.39903164717173</v>
+        <v>32.07295317498975</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35838036801993</v>
+        <v>34.16423488780342</v>
       </c>
       <c r="I6" t="n">
-        <v>3.832070871908701</v>
+        <v>4.910695105467073</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668258202176621</v>
+        <v>4.641879740190682</v>
       </c>
       <c r="K6" t="n">
-        <v>15.44144217634143</v>
+        <v>13.31278419201253</v>
       </c>
       <c r="L6" t="n">
-        <v>42.79406395059562</v>
+        <v>43.63441568817523</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87245697308643</v>
+        <v>99.8366186730335</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.05017069743664</v>
+        <v>85.32812243920642</v>
       </c>
       <c r="C7" t="n">
-        <v>40.72369332087425</v>
+        <v>42.29335369261567</v>
       </c>
       <c r="D7" t="n">
-        <v>1.987555377374087</v>
+        <v>2.028635473391471</v>
       </c>
       <c r="E7" t="n">
-        <v>7.759173454709617</v>
+        <v>8.498156696121629</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478798790784109</v>
+        <v>0.7438899641243667</v>
       </c>
       <c r="G7" t="n">
-        <v>30.28134764853689</v>
+        <v>31.09039129192944</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40247443760691</v>
+        <v>34.21893834972087</v>
       </c>
       <c r="I7" t="n">
-        <v>3.197490655890662</v>
+        <v>4.09879838814136</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674249244240069</v>
+        <v>4.649312275777292</v>
       </c>
       <c r="K7" t="n">
-        <v>16.94982930256336</v>
+        <v>14.67187756079359</v>
       </c>
       <c r="L7" t="n">
-        <v>42.2200309634538</v>
+        <v>42.89836054921666</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89355358689141</v>
+        <v>99.86359180262592</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.96053882714415</v>
+        <v>83.72186792543995</v>
       </c>
       <c r="C8" t="n">
-        <v>43.0696515501382</v>
+        <v>41.32409646570896</v>
       </c>
       <c r="D8" t="n">
-        <v>1.99180239362235</v>
+        <v>1.952994297656905</v>
       </c>
       <c r="E8" t="n">
-        <v>9.6214082487264</v>
+        <v>8.751341036298673</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494779517833793</v>
+        <v>0.7449029767458211</v>
       </c>
       <c r="G8" t="n">
-        <v>30.79899435901638</v>
+        <v>29.93113238010648</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47598578203545</v>
+        <v>34.26553693030777</v>
       </c>
       <c r="I8" t="n">
-        <v>5.63863289331406</v>
+        <v>3.420316699662927</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684237198646121</v>
+        <v>4.655643604661381</v>
       </c>
       <c r="K8" t="n">
-        <v>12.03946117285585</v>
+        <v>16.27813207456006</v>
       </c>
       <c r="L8" t="n">
-        <v>44.70333361264599</v>
+        <v>42.28391594894929</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81244633564003</v>
+        <v>99.88614448921831</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.96038425106077</v>
+        <v>81.91056905695295</v>
       </c>
       <c r="C9" t="n">
-        <v>41.94467183446986</v>
+        <v>40.04411580838517</v>
       </c>
       <c r="D9" t="n">
-        <v>1.901333654248666</v>
+        <v>1.868107714279389</v>
       </c>
       <c r="E9" t="n">
-        <v>9.968971725379417</v>
+        <v>8.84656103782342</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508460708140217</v>
+        <v>0.7457679996783318</v>
       </c>
       <c r="G9" t="n">
-        <v>29.40008741796683</v>
+        <v>28.63018051997272</v>
       </c>
       <c r="H9" t="n">
-        <v>34.538919257445</v>
+        <v>34.30532798520326</v>
       </c>
       <c r="I9" t="n">
-        <v>4.707438182619186</v>
+        <v>2.85357380200625</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692787942587636</v>
+        <v>4.661049997989573</v>
       </c>
       <c r="K9" t="n">
-        <v>14.03961574893923</v>
+        <v>18.08943094304706</v>
       </c>
       <c r="L9" t="n">
-        <v>43.85908372510996</v>
+        <v>41.77144445135492</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84337130851905</v>
+        <v>99.90499120278716</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.65300471942717</v>
+        <v>86.41647004170184</v>
       </c>
       <c r="C10" t="n">
-        <v>40.36767019547244</v>
+        <v>43.12308604575014</v>
       </c>
       <c r="D10" t="n">
-        <v>1.797842604162992</v>
+        <v>1.870242144778213</v>
       </c>
       <c r="E10" t="n">
-        <v>10.08118740613291</v>
+        <v>10.62147619363283</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520215931643178</v>
+        <v>0.7466200864993395</v>
       </c>
       <c r="G10" t="n">
-        <v>27.79981809506445</v>
+        <v>29.93401845750291</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59299328555863</v>
+        <v>35.6156501354705</v>
       </c>
       <c r="I10" t="n">
-        <v>3.929006778066892</v>
+        <v>2.96208748319716</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700134957276988</v>
+        <v>4.666375540620871</v>
       </c>
       <c r="K10" t="n">
-        <v>16.34699528057283</v>
+        <v>13.58352995829817</v>
       </c>
       <c r="L10" t="n">
-        <v>43.15457235221529</v>
+        <v>43.19476043013553</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86923782826057</v>
+        <v>99.90137643418383</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.13427284394655</v>
+        <v>86.10756312656059</v>
       </c>
       <c r="C11" t="n">
-        <v>38.4578332088867</v>
+        <v>43.15476308200611</v>
       </c>
       <c r="D11" t="n">
-        <v>1.685987176848353</v>
+        <v>1.846705551648224</v>
       </c>
       <c r="E11" t="n">
-        <v>10.00040189935593</v>
+        <v>10.97670565785308</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530345497479501</v>
+        <v>0.7473485930713014</v>
       </c>
       <c r="G11" t="n">
-        <v>26.07021144034823</v>
+        <v>29.62611107841345</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63958928840572</v>
+        <v>35.71920749835911</v>
       </c>
       <c r="I11" t="n">
-        <v>3.278582553315694</v>
+        <v>2.520556040519792</v>
       </c>
       <c r="J11" t="n">
-        <v>4.70646593592469</v>
+        <v>4.670928706695634</v>
       </c>
       <c r="K11" t="n">
-        <v>18.86572715605343</v>
+        <v>13.89243687343943</v>
       </c>
       <c r="L11" t="n">
-        <v>42.56730055789136</v>
+        <v>42.86886341014465</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89086092283148</v>
+        <v>99.91606336559018</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>78.48393112753143</v>
+        <v>84.15923572009757</v>
       </c>
       <c r="C12" t="n">
-        <v>36.31465203784583</v>
+        <v>41.59862070237302</v>
       </c>
       <c r="D12" t="n">
-        <v>1.569459722199928</v>
+        <v>1.76341341808893</v>
       </c>
       <c r="E12" t="n">
-        <v>9.765109141593664</v>
+        <v>10.83199098753258</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7539093764279071</v>
+        <v>0.7479708600464162</v>
       </c>
       <c r="G12" t="n">
-        <v>24.26836180411978</v>
+        <v>28.28988181404412</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67983131568374</v>
+        <v>35.74894848323493</v>
       </c>
       <c r="I12" t="n">
-        <v>2.735326164831986</v>
+        <v>2.102212281860492</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711933602674422</v>
+        <v>4.674817875290101</v>
       </c>
       <c r="K12" t="n">
-        <v>21.51606887246858</v>
+        <v>15.84076427990243</v>
       </c>
       <c r="L12" t="n">
-        <v>42.07820735209349</v>
+        <v>42.49059957215457</v>
       </c>
       <c r="M12" t="n">
-        <v>99.9089282624079</v>
+        <v>99.92998455443002</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>75.74488016711655</v>
+        <v>85.2452253955813</v>
       </c>
       <c r="C13" t="n">
-        <v>33.99769549570864</v>
+        <v>42.51743922165782</v>
       </c>
       <c r="D13" t="n">
-        <v>1.450170702648236</v>
+        <v>1.7647659117538</v>
       </c>
       <c r="E13" t="n">
-        <v>9.403186011942259</v>
+        <v>11.44618134601126</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546663981639939</v>
+        <v>0.7485445348519627</v>
       </c>
       <c r="G13" t="n">
-        <v>22.42381043093687</v>
+        <v>28.59055723375472</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71465431554373</v>
+        <v>36.05534481915976</v>
       </c>
       <c r="I13" t="n">
-        <v>2.28172731935649</v>
+        <v>1.961428207225041</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716664988524965</v>
+        <v>4.678403342824766</v>
       </c>
       <c r="K13" t="n">
-        <v>24.25511983288344</v>
+        <v>14.7547746044187</v>
       </c>
       <c r="L13" t="n">
-        <v>41.67120338905148</v>
+        <v>42.66245534078575</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92401871764358</v>
+        <v>99.93466916686226</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>82.78997256203047</v>
+        <v>83.29124312234183</v>
       </c>
       <c r="C14" t="n">
-        <v>38.44556801251279</v>
+        <v>40.86848733746908</v>
       </c>
       <c r="D14" t="n">
-        <v>1.451835869295064</v>
+        <v>1.683374317947438</v>
       </c>
       <c r="E14" t="n">
-        <v>11.86104468155029</v>
+        <v>11.19087853803432</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555329480904331</v>
+        <v>0.7490345081330536</v>
       </c>
       <c r="G14" t="n">
-        <v>24.42129985278147</v>
+        <v>27.27195117639114</v>
       </c>
       <c r="H14" t="n">
-        <v>36.72625676784788</v>
+        <v>36.07894549324043</v>
       </c>
       <c r="I14" t="n">
-        <v>2.851921516900128</v>
+        <v>1.635593412763856</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722080925565209</v>
+        <v>4.681465675831585</v>
       </c>
       <c r="K14" t="n">
-        <v>17.21002743796954</v>
+        <v>16.70875687765816</v>
       </c>
       <c r="L14" t="n">
-        <v>44.24944953158648</v>
+        <v>42.36827166800539</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90504498206882</v>
+        <v>99.94551588313264</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>81.70598565186337</v>
+        <v>82.39767599689048</v>
       </c>
       <c r="C15" t="n">
-        <v>37.80182665223076</v>
+        <v>40.2080066622048</v>
       </c>
       <c r="D15" t="n">
-        <v>1.41149764363845</v>
+        <v>1.645812649298119</v>
       </c>
       <c r="E15" t="n">
-        <v>11.92797863437796</v>
+        <v>11.17182746392386</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7562662045356181</v>
+        <v>0.7494538603337596</v>
       </c>
       <c r="G15" t="n">
-        <v>23.74277142878843</v>
+        <v>26.66342342199541</v>
       </c>
       <c r="H15" t="n">
-        <v>36.76190016970164</v>
+        <v>36.09914454285358</v>
       </c>
       <c r="I15" t="n">
-        <v>2.378907792473668</v>
+        <v>1.383927431399752</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726663778347615</v>
+        <v>4.684086627085997</v>
       </c>
       <c r="K15" t="n">
-        <v>18.29401434813662</v>
+        <v>17.60232400310953</v>
       </c>
       <c r="L15" t="n">
-        <v>43.82493895749653</v>
+        <v>42.1435642325691</v>
       </c>
       <c r="M15" t="n">
-        <v>99.9207799578639</v>
+        <v>99.95389489788342</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>78.95492241754594</v>
+        <v>80.07232801956557</v>
       </c>
       <c r="C16" t="n">
-        <v>35.4178545370888</v>
+        <v>38.0973815614762</v>
       </c>
       <c r="D16" t="n">
-        <v>1.307875866920306</v>
+        <v>1.549621864706709</v>
       </c>
       <c r="E16" t="n">
-        <v>11.38299478335235</v>
+        <v>10.71118589357954</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7568996864527151</v>
+        <v>0.7498138431877674</v>
       </c>
       <c r="G16" t="n">
-        <v>21.99975175691568</v>
+        <v>25.10505915741857</v>
       </c>
       <c r="H16" t="n">
-        <v>36.79269355813545</v>
+        <v>36.11648393326514</v>
       </c>
       <c r="I16" t="n">
-        <v>1.984083725439958</v>
+        <v>1.153826807484299</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730623040329471</v>
+        <v>4.686336519923546</v>
       </c>
       <c r="K16" t="n">
-        <v>21.04507758245407</v>
+        <v>19.92767198043444</v>
       </c>
       <c r="L16" t="n">
-        <v>43.47098710844398</v>
+        <v>41.93650402943937</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93391922798685</v>
+        <v>99.96155757135</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>80.58357313655208</v>
+        <v>84.84482941188128</v>
       </c>
       <c r="C17" t="n">
-        <v>36.61339154664928</v>
+        <v>41.23034902740627</v>
       </c>
       <c r="D17" t="n">
-        <v>1.30893819196274</v>
+        <v>1.55042611492663</v>
       </c>
       <c r="E17" t="n">
-        <v>12.1392843225634</v>
+        <v>12.38497304506902</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7575144798837026</v>
+        <v>0.7502029948653594</v>
       </c>
       <c r="G17" t="n">
-        <v>22.43739385985436</v>
+        <v>26.56614532982567</v>
       </c>
       <c r="H17" t="n">
-        <v>37.24235126050844</v>
+        <v>37.58328501006234</v>
       </c>
       <c r="I17" t="n">
-        <v>1.963625522506311</v>
+        <v>1.321028199223765</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734465499273143</v>
+        <v>4.688768717908495</v>
       </c>
       <c r="K17" t="n">
-        <v>19.41642686344791</v>
+        <v>15.15517058811872</v>
       </c>
       <c r="L17" t="n">
-        <v>43.9047805279753</v>
+        <v>43.57046895300031</v>
       </c>
       <c r="M17" t="n">
-        <v>99.9345989380725</v>
+        <v>99.9559885685253</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>77.90211581446572</v>
+        <v>86.50270676004288</v>
       </c>
       <c r="C18" t="n">
-        <v>34.23439929919262</v>
+        <v>41.98750968057647</v>
       </c>
       <c r="D18" t="n">
-        <v>1.211979862520295</v>
+        <v>1.55172413124301</v>
       </c>
       <c r="E18" t="n">
-        <v>11.5129954446057</v>
+        <v>13.0069605954127</v>
       </c>
       <c r="F18" t="n">
-        <v>0.758045244596838</v>
+        <v>0.750831064606031</v>
       </c>
       <c r="G18" t="n">
-        <v>20.77536563036896</v>
+        <v>26.71314582085461</v>
       </c>
       <c r="H18" t="n">
-        <v>37.26844571336471</v>
+        <v>37.61474972592114</v>
       </c>
       <c r="I18" t="n">
-        <v>1.637501140278989</v>
+        <v>2.172601268217687</v>
       </c>
       <c r="J18" t="n">
-        <v>4.73778277873024</v>
+        <v>4.692694153787693</v>
       </c>
       <c r="K18" t="n">
-        <v>22.09788418553427</v>
+        <v>13.49729323995713</v>
       </c>
       <c r="L18" t="n">
-        <v>43.61317136187017</v>
+        <v>44.44283761651494</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94545484659706</v>
+        <v>99.92764053704853</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>76.79417426031505</v>
+        <v>83.9214367911749</v>
       </c>
       <c r="C19" t="n">
-        <v>33.35734072509594</v>
+        <v>39.74314181938973</v>
       </c>
       <c r="D19" t="n">
-        <v>1.171738017917711</v>
+        <v>1.455721274285654</v>
       </c>
       <c r="E19" t="n">
-        <v>11.36160641791053</v>
+        <v>12.50420667718368</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7585010568262801</v>
+        <v>0.7513713948468174</v>
       </c>
       <c r="G19" t="n">
-        <v>20.08555298486786</v>
+        <v>25.06044334269815</v>
       </c>
       <c r="H19" t="n">
-        <v>37.29085521127995</v>
+        <v>37.64181891329845</v>
       </c>
       <c r="I19" t="n">
-        <v>1.38528896634845</v>
+        <v>1.811803971069534</v>
       </c>
       <c r="J19" t="n">
-        <v>4.740631605164253</v>
+        <v>4.696071217792608</v>
       </c>
       <c r="K19" t="n">
-        <v>23.20582573968496</v>
+        <v>16.07856320882509</v>
       </c>
       <c r="L19" t="n">
-        <v>43.39068498544091</v>
+        <v>44.11794493655691</v>
       </c>
       <c r="M19" t="n">
-        <v>99.9538514502218</v>
+        <v>99.93964996477175</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>74.03500178996049</v>
+        <v>81.25720914129808</v>
       </c>
       <c r="C20" t="n">
-        <v>30.81062725249402</v>
+        <v>37.35915447956381</v>
       </c>
       <c r="D20" t="n">
-        <v>1.073180650264819</v>
+        <v>1.357168316237317</v>
       </c>
       <c r="E20" t="n">
-        <v>10.5984589256669</v>
+        <v>11.90946188643663</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7588954984699563</v>
+        <v>0.7518370565602923</v>
       </c>
       <c r="G20" t="n">
-        <v>18.39611456111581</v>
+        <v>23.36384052109166</v>
       </c>
       <c r="H20" t="n">
-        <v>37.31024749305893</v>
+        <v>37.66514739507683</v>
       </c>
       <c r="I20" t="n">
-        <v>1.155007795946854</v>
+        <v>1.510772362393519</v>
       </c>
       <c r="J20" t="n">
-        <v>4.74309686543723</v>
+        <v>4.698981603501826</v>
       </c>
       <c r="K20" t="n">
-        <v>25.9649982100395</v>
+        <v>18.74279085870192</v>
       </c>
       <c r="L20" t="n">
-        <v>43.18589428840125</v>
+        <v>43.847726773649</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96151975093477</v>
+        <v>99.94967211191472</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>80.42305738690773</v>
+        <v>78.64687944038442</v>
       </c>
       <c r="C21" t="n">
-        <v>34.87410597911746</v>
+        <v>34.98180757418911</v>
       </c>
       <c r="D21" t="n">
-        <v>1.073870252158604</v>
+        <v>1.261127869293186</v>
       </c>
       <c r="E21" t="n">
-        <v>12.75949297955173</v>
+        <v>11.27662655288836</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7593831477513708</v>
+        <v>0.7522384502712579</v>
       </c>
       <c r="G21" t="n">
-        <v>20.30376892051084</v>
+        <v>21.71049092610695</v>
       </c>
       <c r="H21" t="n">
-        <v>39.23005565143082</v>
+        <v>37.6852562114155</v>
       </c>
       <c r="I21" t="n">
-        <v>1.550341762058316</v>
+        <v>1.259649116213799</v>
       </c>
       <c r="J21" t="n">
-        <v>4.746144673446071</v>
+        <v>4.701490314195361</v>
       </c>
       <c r="K21" t="n">
-        <v>19.57694261309226</v>
+        <v>21.35312055961559</v>
       </c>
       <c r="L21" t="n">
-        <v>45.49730653489574</v>
+        <v>43.62310596723992</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94835512710546</v>
+        <v>99.95803410104462</v>
       </c>
     </row>
   </sheetData>
